--- a/reports/דוח נכסים חשודים 02.07.2026.xlsx
+++ b/reports/דוח נכסים חשודים 02.07.2026.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="דוח עסקים חשודים" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,63 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font/>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +89,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="001F4E79"/>
+      </left>
+      <right style="thin">
+        <color rgb="001F4E79"/>
+      </right>
+      <top style="thin">
+        <color rgb="001F4E79"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="001F4E79"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,158 +498,3630 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>דוח עסקים חשודים — עסקים בכתובות מגורים בירושלים</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>מקור: מרשם ארנונה עירייה ירושלים | תאריך: 02.07.2026 | כיסוי: 30–10350 (שלב ג')</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>שם העסק</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>סוג העסק</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>כתובת</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>דירוג חשד</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>כתובת תואמת (מהעירייה)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>שמות בעלי נכסים</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>מס' דירות</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>פירוט החשד</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>סיבת אי-חשד</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>מקור המידע (URL)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ינאי ברק - פיזיותרפיסט</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>קליניקת פיזיותרפיה</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>עלמא 6</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>עלמא 6</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>משה זאב כהן, לינוי מני, יפית סעדון, נטע ברונפמן, מרים גץ צוריאל, ארי לויטס</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>כל 6 היחידות מסווגות 'מגורים'. העסק עשוי לפעול מדירת מגורים ללא סיווג מסחרי.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/80060361/39430/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ואן קובורדן יואל - פיזיותרפיה</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>קליניקת פיזיותרפיה</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>דוד ילין 5</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>גבוה</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ילין דוד 5</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>היהודיה אור חיה המרכז לאישה</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>כל 1 היחידות מסווגות 'מגורים'. העסק עשוי לפעול מדירת מגורים ללא סיווג מסחרי.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>https://www.d.co.il/9996560/39430/</t>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>מינצברג י. הנהלת חשבונות וייעוץ מס</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>הנהלת חשבונות וייעוץ מס</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>אבן האזל 14</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>אבן האזל 14</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/401D0D1A4370655D4D14051046</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>חי שמעון (מגדנית עדו)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>מזון ומגדנייה</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>אגריפס 6</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>אגריפס 6</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/481701164177</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>פוטו תמיר</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>צילום</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>אגריפס 6</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>אגריפס 6</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/48100D114378</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>א.רפי תריסים ואלומיניום</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>תריסים ואלומיניום</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>אבן שפרוט 19</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>אבן שפרוט 19</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>https://kolhair.co.il</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>מתנות קודש יודאיקה גילה</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>מתנות קודש ויודאיקה</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>אבנר חי שאקי 28</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>אבנר חי שאקי 28</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/401D0D1A4370655D411C02104D</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>ינון שירותי מיגון ופריצה</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>מיגון ופריצה</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>אבנר חי שאקי 28</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>אבנר חי שאקי 28</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/401D0D1A4370655D4E1D031444</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>קיי-נט מערכות אלקטרוניקה בע"מ</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>אלקטרוניקה ומערכות</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>אבנר גרשון 9</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>אבנר גרשון 9</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/401D0D1A4370655D4A1C071B40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>אלסברג אושי ודן</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>שירותים</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>אדניהו הכהן 34</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>אדניהו הכהן 34</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/401C041340756D5F4E13001A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>שר היער בע"מ</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>גינון ועיצוב גנים</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>אום טובא 1</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>אום טובא 1</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80193098/43320</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>יואב פק (ייעוץ פיתוח ארגוני)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>ייעוץ פיתוח ארגוני</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>אטינגר 15</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>אטינגר 15</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80095936/19730</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>טווינה פיזותרפיה סינית</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>פיזיותרפיה</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>אטינגר 27</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>אטינגר 27</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/60905910/40030001</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>לובו צביה תיווך</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>תיווך נדל"ן</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>אידלזון אברהם 10</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>אידלזון אברהם 10</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/4520600/32970</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>ד.גרינצוויג קירור ומיזוג</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>קירור ומיזוג</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>אידלזון אברהם 310</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>אידלזון אברהם 310</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80065652/26210</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>דוד הסעות</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>הסעות</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>אלעזר המודעי 4</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>אלעזר המודעי 4</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80028718/870</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>ליעד שירותי אינסטלציה</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>אינסטלציה</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>אלעזר המודעי 4</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>אלעזר המודעי 4</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80040964/2550</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>גלעד גלי - שרה עו"ד</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>עורכת דין</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>אלפסי 21</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>אלפסי 21</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/27624410/9010106</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>פורטמן יהושע (עו"ד)</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>עורך דין</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>אלפסי 28</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>אלפסי 28</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/38169150/38010</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>מיכל בן ארי תכשיטים</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>תכשיטים</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>אלקחי מרדכי 59</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>אלקחי מרדכי 59</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80118658/15640</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>מוניות ניסן אלישע</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>מוניות</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>אלקחי מרדכי 20</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>אלקחי מרדכי 20</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80033932/24060</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>שטרנגר גבי (פסיכולוג קליני)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>פסיכולוג קליני</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>אלקחי מרדכי 20</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>אלקחי מרדכי 20</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/60148150/40270</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>מתי מנעולן</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>מנעולן</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>אלקחי מרדכי 29</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>אלקחי מרדכי 29</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80146893/29970</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>שטוקהמר משה (חשמלאי)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>חשמלאי</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>אלקחי מרדכי 43</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>אלקחי מרדכי 43</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80199276/17910</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>ד"ר בינדלגלס פאול (שיניים)</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>רפואת שיניים</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>אלרואי דוד 3</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>אלרואי דוד 3</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/31655450/46290</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>עו"ד גבאי דניאל</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>עורך דין</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>אמיל זולא 6</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>אמיל זולא 6</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80276756/9010118</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>א.א. אריאל (הדברה)</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>הדברה</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>אנוסי משהד 9</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>אנוסי משהד 9</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/1826340/13110</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>סירקיס אילנה אדריכלית</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>אדריכלות</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>אנוסי משהד 19</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>אנוסי משהד 19</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80072797/630</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>הללי שאול (גרפולוגיה)</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>גרפולוגיה</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>אנוסי משהד 1</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>אנוסי משהד 1</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/18137990/11330</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>מאור הובלה ואחסנה</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>הובלה ואחסנה</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>אנוסי משהד 1</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>אנוסי משהד 1</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80073226/35840</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>אפקטיבי הדברות</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>הדברה</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>אנילביץ 62</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>אנילביץ 62</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80012503/13110</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>בית חם הסקות ומיזוג</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>הסקה ומיזוג</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>אנילביץ 64</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>אנילביץ 64</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80115839/26210</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>ד"ר לילי זמיר</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>רפואה</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>אנילביץ 54</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>אנילביץ 54</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr"/>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80062753/19745</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>אייקידו</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>אומנויות לחימה</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>ארלוזורוב 10</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>ארלוזורוב 10</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/30829140/3315</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>גישור נדל"ן</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>תיווך נדל"ן</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>ארלוזורוב 18</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>ארלוזורוב 18</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>ד"ר יורש מינה</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>רפואה</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>ביאליק 12</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>ביאליק 12</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/68972270/46290</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>א.פטרוב מדידות הנדסה בע"מ</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>מדידות הנדסה</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>ביצור יהושע 3</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>ביצור יהושע 3</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80263315/23790</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>ניהול זמן; עכשיו</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>ייעוץ ניהול</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>ביצור יהושע 6</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>ביצור יהושע 6</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80176237/3530</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>איריס סיוון</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>טיפולים</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>ביצור יהושע 5</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>ביצור יהושע 5</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80045982/39740</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>אלי קופות רושמות</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>קופות רושמות</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>בית הכרם 25</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>בית הכרם 25</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/33700790/43980</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>הכל ליולדת</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>מוצרי תינוקות ויולדות</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>בית וגן 54</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>בית וגן 54</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80147036/9010097</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>הכיף שבאפייה</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>אפייה</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>בית וגן 61</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>בית וגן 61</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80204687/24760</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>שפיגל ישראל</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>שירותים</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>בית וגן 103</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>בית וגן 103</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr"/>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/5892000/38190</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>ברוכין אהרון</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>עורך דין</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>בלפור 10</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>בלפור 10</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/9838580/38010</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>חגית את דרור בע"מ</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>אופנה ועיצוב</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>בצלאל 31</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>בצלאל 31</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/19891020/49230</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>בודרה דויד</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>שירותים</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>בצלאל 24</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>בצלאל 24</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80051399/8450</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>אחדות ירוחם</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>שירותים</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>בר כוכבא 26</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>בר כוכבא 26</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/9604430/38775</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>דיפתרן - חשבונאות וניהול בע"מ</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>הנהלת חשבונות</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>בר גיורא 5</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>בר גיורא 5</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/1447330/13890</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>המרכז לעירובים באר"ק</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>שירותי דת</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>בר גיורא 4</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>בר גיורא 4</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80077093/300</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>אולפני סינטי סאונד</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>אולפן הקלטות</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>בר יוחאי 9</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>בר יוחאי 9</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/8917960/1110</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>רחמים שמעון</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>שירותים</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>ברוריה 7</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>ברוריה 7</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr"/>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/28597830/23910</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>אורנג' מירה</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>תקשורת</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>ברכת אברהם 16</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>ברכת אברהם 16</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr"/>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80248063/14165</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>מחסן הבשר</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>קצביה</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>ברכת אברהם 4</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>ברכת אברהם 4</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr"/>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80012629/2490</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>גני אל</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>גינון</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>גבריהו חיים 11</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>גבריהו חיים 11</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/76736270/27840</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>בוזו רפי</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>שירותים</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>גבריהו חיים 11</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>גבריהו חיים 11</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr"/>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/72821890/9880</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>טיימינג הובלות</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>הובלות</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>גדוד החמישי 11</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>גדוד החמישי 11</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr"/>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80170085/35840</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>אליעזר טכנאי מחשבים</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>טכנאי מחשבים</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>גדוד החמישי 24</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>גדוד החמישי 24</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80001072/25805</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>ד"ר בלאושילד נועם</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>רפואה</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>גדוד החמישי 6</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>גדוד החמישי 6</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr"/>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80167338/46230</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>דוד שירותי צבע</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>שירותי צביעה</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>גדוד חרמש 16</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>גדוד חרמש 16</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr"/>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80087602/41160</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>מדיה ווייז</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>מדיה ופרסום</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>גדוד חרמש 16</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>גדוד חרמש 16</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr"/>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/7351750/40920</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>שרה יופי של אומנות</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>יופי ואומנות</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>גדוד חרמש 19</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>גדוד חרמש 19</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr"/>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80249291/14690</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>ארוך חיים</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>שירותים</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>גדוד חרמש 19</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>גדוד חרמש 19</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr"/>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/28372680/13890</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>עמנואל הובלות</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>הובלות</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>גדוד מכמש 4</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>גדוד מכמש 4</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/76596590/35840</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>המרכז הארצי לדלתות פלדה</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>דלתות פלדה</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>גדוד מכמש 19</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>גדוד מכמש 19</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/70926950/12380</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>גבי מינצברג</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>טיפולים ורפואה</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>גבעת בית הכרם 4</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>גבעת בית הכרם 4</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80305721/40030014</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>טליס - tali's</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>אופנה ובגדים</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>גבעת קנדה 16</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>גבעת קנדה 16</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80068899/3970</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>ד"ר לביא אמיר</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>רפואה</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>גבעת קנדה 21</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>גבעת קנדה 21</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr"/>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80034544/46860</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>יואל רות</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>טיפולים</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>גדליה 3</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>גדליה 3</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr"/>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/65122630/40030057</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>מירון יעוץ לוגיסטי ושיווק</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>ייעוץ לוגיסטי ושיווק</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>גואטמאלה 16</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>גואטמאלה 16</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80097907/19770</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>שירה מאפרת כלות וערב</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>איפור וסטיילינג</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>גולומב 23</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>גולומב 23</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr"/>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80291219/2800</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>לויתן בני</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>שירותים</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>גלבר 14</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>גלבר 14</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/71620430/9880</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>גל-יה סוכנות נכסים</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>תיווך נדל"ן</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>גלעדי 8</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>גלעדי 8</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr"/>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80073953/32970</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>אילוז אילן-משולש</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>שירותים</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>גבירצמן משה 17</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>גבירצמן משה 17</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr"/>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>https://d.co.il/7249710/41280</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>מקסים חשמלאי</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>חשמלאי</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>גולומב 23</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>גולומב 23</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>נמצא בחיפוש אינטרנט בכתובת מגורים ממרשימת הארנונה</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>https://d.co.il/80336724/17910</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="40" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>הערות: עסקים שנמצאו בחיפוש אינטרנט בכתובות מגורים מרשימת ארנונה עיריית ירושלים | מספרי מקשר וירטואלי (072) לא נכללו | ייתכן עסקים נוספים שאינם ברשומות ציבוריות</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J42" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J52" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J71" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J72" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J73" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J74" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J75" r:id="rId72"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>